--- a/output/广义投诉流量202605_test_5_summary.xlsx
+++ b/output/广义投诉流量202605_test_5_summary.xlsx
@@ -443,12 +443,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>费用争议</t>
+          <t>流量问题</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>流量超套扣费</t>
+          <t>流量提醒不到位</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -463,12 +463,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>费用争议</t>
+          <t>流量问题</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>账单异常</t>
+          <t>流量超套扣费</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -502,7 +502,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>费用争议</t>
+          <t>流量问题</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -572,7 +572,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>费用争议</t>
+          <t>流量问题</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
